--- a/outputs/227-40.xlsx
+++ b/outputs/227-40.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t xml:space="preserve">Site Name</t>
   </si>
@@ -149,16 +149,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -394,206 +398,220 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="10.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="10.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="0" t="str">
-        <f aca="false">IF(A2=B2,"",B2)</f>
-        <v>Adam</v>
-      </c>
-      <c r="C14" s="0" t="str">
-        <f aca="false">IF(B2=C2,"",C2)</f>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B2:C2,C2)=1,C2,"")</f>
         <v>Martin</v>
       </c>
-      <c r="D14" s="0" t="str">
-        <f aca="false">IF(C2=D2,"",D2)</f>
+      <c r="D15" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B2:D2,D2)=1,D2,"")</f>
         <v>Alex</v>
       </c>
-      <c r="E14" s="0" t="str">
-        <f aca="false">IF(D2=E2,"",E2)</f>
+      <c r="E15" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B2:E2,E2)=1,E2,"")</f>
         <v>Bob</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B15" s="0" t="str">
-        <f aca="false">IF(A3=B3,"",B3)</f>
-        <v>Joe</v>
-      </c>
-      <c r="C15" s="0" t="str">
-        <f aca="false">IF(B3=C3,"",C3)</f>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B3:C3,C3)=1,C3,"")</f>
         <v>Dan</v>
       </c>
-      <c r="D15" s="0" t="str">
-        <f aca="false">IF(C3=D3,"",D3)</f>
+      <c r="D16" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B3:D3,D3)=1,D3,"")</f>
         <v>Jack</v>
       </c>
-      <c r="E15" s="0" t="str">
-        <f aca="false">IF(D3=E3,"",E3)</f>
+      <c r="E16" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B3:E3,E3)=1,E3,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="0" t="str">
-        <f aca="false">IF(A4=B4,"",B4)</f>
-        <v>Oliver</v>
-      </c>
-      <c r="C16" s="0" t="str">
-        <f aca="false">IF(B4=C4,"",C4)</f>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B4:C4,C4)=1,C4,"")</f>
         <v/>
       </c>
-      <c r="D16" s="0" t="str">
-        <f aca="false">IF(C4=D4,"",D4)</f>
+      <c r="D17" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B4:D4,D4)=1,D4,"")</f>
         <v>Nick</v>
       </c>
-      <c r="E16" s="0" t="str">
-        <f aca="false">IF(D4=E4,"",E4)</f>
+      <c r="E17" s="1" t="str">
+        <f aca="false">IF(COUNTIF($B4:E4,E4)=1,E4,"")</f>
         <v/>
       </c>
     </row>
